--- a/AAII_Financials/Quarterly/BMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BMA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>BMA</t>
   </si>
@@ -656,335 +656,342 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3">
         <v>945100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>568500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>892600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>791300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1375800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1126400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>920800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3123600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3867600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3145600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4651800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3692500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>270000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>142600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>224300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>228500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>450600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>393600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>812800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>512000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>492600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>408400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>870500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>485300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>646500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>525600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>979700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>491300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>293900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>228100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>199300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>187400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>239600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>203500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>179400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>195300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>198300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>194100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
         <v>12500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1060,50 +1067,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>932700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>557800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>879900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>779600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1354200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1108400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>901600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3104900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3846000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3117100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4609000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3652800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1179,8 +1189,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1235,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,8 +1355,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,44 +1477,47 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>89600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>26000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1579,127 +1599,133 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E15" s="3">
         <v>34400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>31300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>32000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>43400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>43800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>51300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>88600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>103200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>90800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-3400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-6600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-7300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-14500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-13100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-24700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-14600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-25200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>-2500</v>
       </c>
       <c r="AH15" s="3">
         <v>-2500</v>
       </c>
       <c r="AI15" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1764,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
         <v>717700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>596700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>670500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>711600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1149700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>963600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1469000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2415300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2436300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2978200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3584800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3350000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>152300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>78400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>96200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>92100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>187400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>161000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>367900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>241900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>248600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>193400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>322300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>164900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>249300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>234600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>490200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>252200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>152500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>98000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>74600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>65500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>79300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>71700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>64600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>69100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>96500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>96400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>227400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>222000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>79700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>226100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>162800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-548200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>708300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1431300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>167300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1067000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>342500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>117700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>64200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>128000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>136500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>263200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>232600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>444900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>270000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>244100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>215000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>548300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>320400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>397100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>290900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>489500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>239000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>141300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>130100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>124700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>121900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>160300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>131700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>114800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>126200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>101800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>97600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,246 +2052,253 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-407000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-89200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-46900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-108900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-111300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-205800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-172300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-351000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-218900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-179700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-126200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-268900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-152800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-228100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-208000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-288200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-114200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-54800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-60200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-36100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-62700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-33700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-35900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-44500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-35400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-31300</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E21" s="3">
         <v>261200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>254400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>111300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>270100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>210500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-503800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>752000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1889600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>255300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1166600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>428500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>34300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>24600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>71900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>77800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>114200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>63600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>101900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>302500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>179500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>183100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>94000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>218800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>134400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>95800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>77800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>67100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>101700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>101400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>81800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>85100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>66600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2298,8 +2338,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2376,246 +2416,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>137200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>222400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>79200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>200600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>164200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-547600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>707800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1831700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>167900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1063400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>337700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>28500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>57400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>60300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>94000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>51100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>64300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>88800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>279400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>167600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>169000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>82900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>201300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>124900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>93100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>75300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>64500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>85800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>97600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>98000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>78800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>81700</v>
-      </c>
-      <c r="AN23" s="3">
-        <v>66400</v>
       </c>
       <c r="AO23" s="3">
         <v>66400</v>
       </c>
+      <c r="AP23" s="3">
+        <v>66400</v>
+      </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>58700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>87000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>34000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>47800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>40100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-210500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>172600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>581700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>101600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>325400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>122500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>33300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>35100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>94700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>61900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>69800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>119500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>73800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>29000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>25800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>34900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>27400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>28700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>22000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>23600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2782,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E26" s="3">
         <v>78500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>135400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>152800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>124100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-337000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>535300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1250000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>66300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>738000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>215100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>71600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>58000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>60700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>48400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>53700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>184700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>105700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>99200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>81800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>51100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>64100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>52000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>45900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>58900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>71800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>63200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>51500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>53000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>44400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="3">
         <v>78700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>135000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>44300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>152500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>123500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-337800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>535600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1249400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>66100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>737500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>214800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>71600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>58000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>60700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>48400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>53700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>184700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>105700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>99200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>93700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>81800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>51100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>64700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>51900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>45600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>71200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>62700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>51000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>52500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>44400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3148,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3270,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3392,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3514,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>407000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>89200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>46900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>108900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>111300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>205800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>172300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>351000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>218900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>179700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>126200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>268900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>152800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>228100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>208000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>288200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>114200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>48200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>54800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>60200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>62700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>33700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>35900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>44500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>35400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>31300</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E33" s="3">
         <v>78700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>135000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>44300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>152500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>123500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-337800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>535600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1249400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>66100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>737500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>214800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>71600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>58000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>60700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>48400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>53700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>184700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>105700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>99200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>93700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>81800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>51100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>64700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>51900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>45600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>71200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>62700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>51000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>52500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>44400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3880,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E35" s="3">
         <v>78700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>135000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>44300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>152500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>123500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-337800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>535600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1249400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>66100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>737500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>214800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>71600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>58000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>60700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>48400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>53700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>184700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>105700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>99200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>93700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>81800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>51100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>64700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>51900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>45600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>71200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>62700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>51000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>52500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>44400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4175,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,288 +4219,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1015300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>970700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>972300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1041500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1262700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2033300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>791300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1240300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2339400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1883100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3138900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3704700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>178000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>138900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>132000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>364100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>734700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>511100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>425800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>620800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>710400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>629900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>536100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>896600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1045100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>724200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>842100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>812600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>757200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>807800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>661100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>454500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>823900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>700900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>660600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>744300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>924100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>607900</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E42" s="3">
         <v>800200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>490400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>677700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>747700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>982200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1093800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4978600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5075900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6061200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2768500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2819500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1565400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>372000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>326100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>195300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>269400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>585800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>410800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>525600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>668200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1426200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>715100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1065800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>360600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>526400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>321400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>214600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>173100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>210900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>164000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>136800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>432500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>396500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>357300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>163500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>188700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>176500</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E43" s="3">
         <v>468900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>452500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>437000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>450300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>745200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1059600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>383500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>220400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>472100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>493400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>475600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>366900</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4490,8 +4583,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4531,8 +4627,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4609,50 +4705,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>97600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>105300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>96900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>86400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>140000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>87300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>83000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>80200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>157200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>69500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>67600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>69100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4728,50 +4827,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4480100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3588500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3421900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3634500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5521000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5886400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7309300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7160000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10444600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5841200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7093500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6573500</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4847,118 +4949,121 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2984400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2659900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3103100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3018200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3968300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2939200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>625000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>570200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1121300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>541400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>895600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>784900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14700</v>
-      </c>
-      <c r="U47" s="3">
-        <v>10700</v>
       </c>
       <c r="V47" s="3">
         <v>10700</v>
       </c>
       <c r="W47" s="3">
+        <v>10700</v>
+      </c>
+      <c r="X47" s="3">
         <v>14400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>17600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>15000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>17400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>23500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>16900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>17300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>20100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>11500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>800</v>
-      </c>
-      <c r="AM47" s="3">
-        <v>300</v>
       </c>
       <c r="AN47" s="3">
         <v>300</v>
@@ -4966,246 +5071,255 @@
       <c r="AO47" s="3">
         <v>300</v>
       </c>
+      <c r="AP47" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>161700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>154900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>172000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>798500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>216900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>163000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>147300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>130700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>194200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>115300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>111400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>105900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>90000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>74200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>291500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>207500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>186900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>242500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>323700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>224900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>245400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>273400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>360300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>109900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>107300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>121500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>111100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>107200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>111100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>119600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>161500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>35600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>34100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>39400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>38200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>34700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>126000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>126400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>141000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>150000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>188200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>145000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>140900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>128800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>202500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>102200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>105200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>104400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>12600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>27500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>46300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>32500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>28700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>36300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>48100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>32300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>35200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>39200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>49600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>19800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>19100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>17300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>15600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>14500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>15700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>40500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>19200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>17700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>19900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>17400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5437,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,113 +5559,116 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>870700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1091600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>899500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>293500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1198200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>856700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>802700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>757800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1204500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>702900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>710000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>721100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>18000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>19900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>25100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10500</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>2500</v>
       </c>
       <c r="AH52" s="3">
         <v>2500</v>
       </c>
       <c r="AI52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5200</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5561,8 +5681,11 @@
       <c r="AO52" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP52" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5803,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16011700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15003900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15488000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15044300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18491400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14681100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12830400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11660400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18097700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10594300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12391200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11628100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2174100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1835700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1431200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3228000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5500000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3875200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3494900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4778600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7251500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5319700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5334300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5027300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6208800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4139300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4255000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4816300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4230600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4222300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3978200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3829400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5192200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4733600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4307400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4371900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4057900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3580900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5971,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,169 +6015,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E57" s="3">
         <v>9432700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8613700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8907500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8973900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10746800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8325300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7390600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5873000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9077700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5740000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7413500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7006800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>140500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>88400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>74500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>169100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>371500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>174000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>311200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>463600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>208500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>245600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>233000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>310300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>171800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>157400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>205100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>189000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>173600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>163900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>150300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>374000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>219100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>219900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>222000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>239200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>182100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>518400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>269000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>78800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>60300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>116000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>106700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>83200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>127200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>293300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>156200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>64000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>57900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6123,118 +6257,121 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1543200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1188500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1555100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1049700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1307300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1740500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1136400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>997200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1842500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1174900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1353200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>874700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>29500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>48500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>72500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>63900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>102100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>113900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>46300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>44000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>56400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>36400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>28600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>26100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>67300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>91200</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM59" s="3" t="s">
-        <v>5</v>
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM59" s="3">
+        <v>0</v>
       </c>
       <c r="AN59" s="3" t="s">
         <v>5</v>
@@ -6242,50 +6379,53 @@
       <c r="AO59" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E60" s="3">
         <v>11681300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10263600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10703900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10232300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12416100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10350200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8744600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7143400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11497400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7191500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8950000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8047200</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6361,246 +6501,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
         <v>527900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>930700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>804000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>427200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>535000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>413600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>425200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>431600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>899200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>409800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>410900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>428000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>80400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>68400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>57500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>144700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>250300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>190400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>182000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>276800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>378100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>271100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>294900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>326700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>449000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>340100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>271400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>336400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>304400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>360300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>316200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>225800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>308600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>285000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>270200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>166300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>211200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>104400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>195300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>183600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>40900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>139200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>269600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>112500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>116000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>41900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>49200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>27100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>40400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>39600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>59200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>71500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>45000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>15700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>27300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>11000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>8600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>9200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>8800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6867,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +6989,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7111,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>131100</v>
+      </c>
+      <c r="E66" s="3">
         <v>12405200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11530700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11696200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10904700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13322900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10924900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9328600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7741300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12604800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7715200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9496700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8600100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1641200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1393900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1078300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2429000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4184800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2983700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2708400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3717500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5856800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4344700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4317500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3846100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4741300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3354200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3589400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4050100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3556400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3530700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3244100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3001500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4124700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3813200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3485500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3746900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3479100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3046600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7279,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7399,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7521,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7643,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7765,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2459400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2347500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2573900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2870100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3566200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2571000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2349300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2838500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3820100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1796500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1795600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1945700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>339100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>276600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>217400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>484700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>787700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>517400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>444200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>614300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>797700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>560500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>565700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>683300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>815900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>650700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>526600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>604400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>512500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>513800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>542300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>611300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>881500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>613400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>553800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>599000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>552900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>508500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8009,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8131,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8253,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3604500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3470900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3789300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4136700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5166400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3755300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3500900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3918800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5491700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2878600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2894200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3027500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>532900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>441800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>352900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>799000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1315100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>891500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>786600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1061000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1394700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>975000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1016800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1181200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1467500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>785100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>665600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>766100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>674200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>691600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>734100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>827900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1067500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>920300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>821900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>624900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>578700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>534400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8497,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E81" s="3">
         <v>78700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>135000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>44300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>152500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>123500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-337800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>535600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1249400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>66100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>737500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>214800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>71600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>58000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>60700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>48400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>53700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>184700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>105700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>99200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>93700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>81800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>51100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>64700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>51900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>45600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>71200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>62700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>51000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>52500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>44400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8792,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E83" s="3">
         <v>57200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>46400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>43800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>61900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>88600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>90800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>120600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>54000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>40400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>23100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2600</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>2500</v>
       </c>
       <c r="AH83" s="3">
         <v>2500</v>
       </c>
       <c r="AI83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>3300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>3000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>3400</v>
       </c>
-      <c r="AN83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AO83" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP83" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9034,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9156,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9278,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9400,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9522,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>-93100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-69800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-761900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-854300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-399300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1776100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-419400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>326600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>724400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3702900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1198600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5468500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>40600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>33200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>56900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-104300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-269100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-176200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>138400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>511700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>107500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-30900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-546700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>621800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>493200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>240700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>129100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>554900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>38600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>50500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-394400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>104700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>7500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-92100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>237600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9690,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-33800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-78000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-93700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-96800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7145000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10466600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5183800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1531100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3640300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4657400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3125900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2600</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9932,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10054,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-59500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>307600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-78000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-93700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-96800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-8200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-7200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,59 +10222,60 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3">
         <v>8200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>80000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>28500</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3">
         <v>43400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>218500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>391900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>1100</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-5800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-7600</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -10073,11 +10307,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-67800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -10106,10 +10340,13 @@
         <v>0</v>
       </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-16800</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10464,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10586,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10708,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>737400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>534300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>719400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>451900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-393600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>535600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>729300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-154200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1186400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4969300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>887500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2067000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-22200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-89600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-39800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-69400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>47000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>337200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>95100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-18900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E101" s="3">
         <v>205900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>101400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>83400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>110400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1347300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1272700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1108600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>769500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1219200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>995600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>354500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>197200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>53900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>45500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>32000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>30300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>45600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>52400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>105600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>101600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>93200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>88100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>145000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>69300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>349300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>89700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>102200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-42100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>159800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>99400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>33900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>40700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>10300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>27000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>772600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>643200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>71000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-359200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-646400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2367400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>350500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>246500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1192900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-71700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>703900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4074100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>68300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>49100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>86900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-96400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-240300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-120100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>202800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>589800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>138200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-328800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>576100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>553400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>149500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>210900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>647800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>50200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>51200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-288400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>352000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-36300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>22800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>238500</v>
       </c>
     </row>
